--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_014/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_014/extracted.xlsx
@@ -485,6 +485,16 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="I3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -595,6 +605,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -670,6 +685,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G5" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H5" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -736,11 +756,6 @@
       </text>
     </comment>
     <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1146,6 +1161,11 @@
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1423,17 +1443,17 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>RF Ablation Catheter CHT Model — Sprint M6</t>
+          <t>RF Ablation Catheter CHT V&amp;V (Sprint M6)</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Inform safe power/irrigation envelopes for a 7F open-irrigated RF ablation catheter in the left atrium with esophagus 3–5 mm posterior</t>
+          <t>Predict peak tissue temperature and lesion geometry to set safe power/irrigation envelopes for a 7F open-irrigated RF ablation catheter in the left atrium</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>A 3D conjugate thermal-fluid model predicts peak tissue temperature at 3 mm depth and lesion depth/width after 30–60 s RF application (25–45 W, 17–30 mL/min irrigation, atrial blood speed 0.15–0.25 m/s). Results directly inform the IFU power/irrigation table. High consequence of error (thermal injury to esophagus); medium–high model influence on clinical limits.</t>
+          <t>A 3D conjugate thermal-fluid model with Joule heating is used to inform the IFU power/irrigation table for a 7F open-irrigated RF ablation catheter operating in the left atrium with the esophagus 3–5 mm posterior. Decision metrics are peak tissue temperature at 3 mm depth and lesion depth/width after 30–60 s at 25–45 W and 17–30 mL/min. Consequence of error is high (thermal injury risk); model influence is medium–high.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1461,15 +1481,19 @@
           <t>ASME-VV40-2018</t>
         </is>
       </c>
-      <c r="I3" s="22" t="n"/>
+      <c r="I3" s="39" t="inlineStr">
+        <is>
+          <t>CHT V&amp;V Team</t>
+        </is>
+      </c>
       <c r="J3" s="22" t="inlineStr">
         <is>
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2075,7 +2099,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Model predictions of peak tissue temperature at 3 mm depth and lesion depth/width must fall within the validated 95% total-error band across the clinical operating envelope (25–45 W, 17–30 mL/min, 0.15–0.25 m/s blood speed, 10–30 g contact force) to support IFU table generation without exceeding thermal injury thresholds; a 5 C safety margin is retained on the 3 mm temperature threshold.</t>
+          <t>Peak tissue temperature at 3 mm depth and lesion depth/width predictions must fall within the validated uncertainty band across the clinical operating envelope (25–45 W, 17–30 mL/min, blood speed 0.15–0.25 m/s, contact force 10–30 g) with a 5 C safety margin on the 3 mm temperature threshold, to ensure no thermal injury to esophagus or myocardium beyond intended lesion.</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2103,7 +2127,7 @@
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023 R2 model with custom UDF (rfcht-v1.7) solving incompressible thermal-fluid flow, quasi-static Joule heating with temperature-dependent electrical conductivity, Pennes perfusion term, and saline irrigation jets across a 20×20×15 mm myocardial domain.</t>
+          <t>Ansys Fluent 2023 R2 model with custom UDF for Joule heating and Pennes perfusion; solves incompressible conjugate heat transfer in blood, saline irrigation, electrode, epoxy, and myocardium with temperature-dependent electrical and thermal properties.</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2123,7 +2147,7 @@
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>12 porcine perfused-myocardium benchtop tests (25–45 W, 17–30 mL/min, two blood speeds) with fiber-optic temperature probes at 3 and 5 mm depth and lesion dimensions from 7T MRI (0.2 mm voxel); three additional training cases used solely for calibration.</t>
+          <t>12 porcine myocardium test cases (25–45 W, 17–30 mL/min, two blood speeds) with fiber-optic temperature probes at 3 mm and 5 mm depth and 7T MRI lesion dimensions; 3 additional training cases used for calibration only.</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2137,13 +2161,13 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>UQ Latin Hypercube Propagation Dataset</t>
+          <t>Latin Hypercube Uncertainty Propagation Dataset</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>N=200 Latin Hypercube samples propagating uncertainty in tissue thermal/electrical properties (±15%), contact pressure, blood speed, irrigation rate, and esophageal wall temperature through the verified mesh/time-step configuration; global Sobol indices computed.</t>
+          <t>N=200 LHS runs propagating tissue thermal/electrical properties (±15%), contact pressure (10–20 kPa), blood speed, irrigation rate, and esophageal wall temperature through the verified model to compute Sobol sensitivity indices and total-uncertainty intervals.</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
@@ -2293,7 +2317,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Code Verification — Custom UDF Benchmark</t>
+          <t>Benchtop Temperature Prediction Validation</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2308,27 +2332,27 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Custom heat-source UDF and perfusion toggle exercised against a closed-form temperature field with an artificially forced source; energy residual over the control volume checked at steady state.</t>
+          <t>Model predictions of peak tissue temperature at 3 mm depth compared against fiber-optic probe measurements in 12 blinded perfused-porcine-myocardium benchtop tests spanning the clinical power and irrigation envelope.</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>Analytical closed-form temperature field (manufactured source)</t>
+          <t>Fiber-optic temperature measurements (±0.3 C, k=2) at 3 mm and 5 mm depth across 12 test cases</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G3" s="22" t="inlineStr">
-        <is>
-          <t>Quantitative result if applicable</t>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G3" s="39" t="inlineStr">
+        <is>
+          <t>Total-error band combining model uncertainty (LHS/Sobol) and experimental measurement uncertainty (±0.3 C k=2); 95th-percentile absolute error reported</t>
         </is>
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>Energy residual &lt; 0.2% at steady state; UDF unit tests pass CI on each commit</t>
+          <t>Mean absolute error 2.1 C; 95th-percentile absolute error 4.0 C; all cases within pre-specified 95% total-error band except one outlier at 45 W/0.15 m/s (depth under-prediction 15%, attributed to charring not modeled)</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2340,7 +2364,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Spatial Mesh Convergence Study</t>
+          <t>Benchtop Lesion Geometry Validation</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2351,27 +2375,27 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Four meshes (1.2M to 9.6M cells) with local refinement at electrode/tissue interface (minimum cell 20 µm); second-order discretization, coupled solver. Observed order of accuracy and Richardson-extrapolated discretization errors computed for peak temperature and lesion depth.</t>
+          <t>Model predictions of lesion depth and width compared against 7T MRI measurements (0.2 mm voxel) from the same 12 blinded benchtop test cases.</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / observed order of accuracy</t>
+          <t>7T MRI lesion dimensions (±0.2 mm measurement uncertainty)</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G4" s="41" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / observed order analysis</t>
+          <t>Normalized RMSE; measurement uncertainty ±0.2 mm propagated into comparison band</t>
         </is>
       </c>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>Observed order 1.96 for peak temperature; extrapolated discretization effect 3.8% on peak temp, 2.6% on lesion depth</t>
+          <t>Normalized RMS error on lesion depth 9%; lesion width 11%; one outlier at 45 W/0.15 m/s under-predicts depth by 15%</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2383,7 +2407,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Temporal Convergence Study</t>
+          <t>Spatial Mesh Convergence Study</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2394,23 +2418,27 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Time-step halving from 5 ms to 2.5 ms; peak temperature shift evaluated to confirm 5 ms time step is adequate.</t>
+          <t>Four meshes (1.2M to 9.6M cells) with local refinement at electrode/tissue interface (min cell 20 µm); second-order discretization; observed convergence order and discretization error estimated for peak temperature and lesion depth.</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>Halved time-step solution</t>
+          <t>Richardson extrapolation / observed-order analysis</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G5" s="33" t="n"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G5" s="41" t="inlineStr">
+        <is>
+          <t>Observed-order calculation (p=1.96 for peak temperature); extrapolated discretization error reported</t>
+        </is>
+      </c>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>Peak temperature shift 0.6 C on halving; 5 ms retained</t>
+          <t>Observed order 1.96; extrapolated discretization effect 3.8% on peak temperature, 2.6% on lesion depth</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2422,7 +2450,7 @@
     <row r="6" ht="15" customHeight="1" s="18">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>Iterative Solver Convergence Monitoring</t>
+          <t>Temporal Convergence Study</t>
         </is>
       </c>
       <c r="B6" s="41" t="inlineStr">
@@ -2433,12 +2461,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Residual targets and integral energy plateau monitored throughout all simulations to confirm iterative solver convergence.</t>
+          <t>Time-step halving from 5 ms to 2.5 ms assessed for sensitivity of peak tissue temperature; 5 ms time step retained.</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Convergence targets specified in modeling plan</t>
+          <t>Halved time-step solution</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2449,7 +2477,7 @@
       <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Residuals &lt; 1e-6; integral energy plateau within 0.3% over last 10 s</t>
+          <t>Peak temperature shift 0.6 C upon time-step halving; 5 ms retained</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2461,7 +2489,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Benchtop Validation — Temperature and Lesion Predictions vs. Experiment</t>
+          <t>UDF Benchmark and Code Verification</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2472,27 +2500,23 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>Model predictions of tissue temperature at 3 mm depth and lesion depth/width compared against 12 blinded porcine benchtop tests spanning the clinical operating envelope. Calibration was frozen before validation runs. One outlier at 45 W/0.15 m/s under-predicts depth by 15% (char layer not modeled).</t>
+          <t>Custom Joule-heating UDF and perfusion toggle verified against a closed-form benchmark with artificially forced temperature field and tailored source term; energy balance checked over the control volume.</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>Fiber-optic probe temperatures (±0.3 C, k=2) and 7T MRI lesion dimensions (±0.2 mm) from 12 blinded validation cases</t>
+          <t>Closed-form analytical benchmark temperature field</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="41" t="inlineStr">
-        <is>
-          <t>Combined model and test uncertainty; 95% total-error band; Latin Hypercube UQ propagation (N=200); Global Sobol sensitivity indices</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" s="33" t="n"/>
       <c r="H7" s="41" t="inlineStr">
         <is>
-          <t>Mean absolute temperature error at 3 mm = 2.1 C; 95th percentile error 4.0 C; NRMSE lesion depth 9%, lesion width 11%; all cases within 95% total-error band except one 45 W outlier</t>
+          <t>Control-volume energy residual &lt;0.2% at steady state; UDF unit tests pass CI on each commit</t>
         </is>
       </c>
       <c r="I7" s="42" t="inlineStr">
@@ -2515,12 +2539,12 @@
       <c r="C8" s="33" t="n"/>
       <c r="D8" s="41" t="inlineStr">
         <is>
-          <t>External SME (Dr. R. Ghuman) performed red-team review and re-ran one validation case from scratch on a different workstation under configuration-controlled containerized workflow.</t>
+          <t>External SME (Dr. R. Ghuman) re-ran one validation case from scratch on a separate workstation using the containerized workflow to verify reproducibility of peak temperature and lesion depth predictions.</t>
         </is>
       </c>
       <c r="E8" s="41" t="inlineStr">
         <is>
-          <t>Primary team simulation results</t>
+          <t>Original model run results</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
@@ -2745,12 +2769,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercial solver with traceable versioning; custom code under version control with CI testing; containerized reproducible execution environment</t>
+          <t>Simulation software and custom code must have documented version control, regression/unit testing, and configuration management sufficient for a high-consequence medical device application.</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023 R2 used as the base solver (commercial, widely validated). Custom UDF tracked under Git tag rfcht-v1.7 (commit 9f4a1b2) with unit tests passing CI on every commit. Run scripts executed inside a Singularity container (SHA hash 3c7…9a1). Input decks, meshes, and outputs tracked by DVC with SHA links to raw data. This constitutes thorough SQA with version control, automated testing, and reproducibility controls.</t>
+          <t>Ansys Fluent 2023 R2 is a commercial solver with established QA pedigree. Custom UDF is tracked under Git tag rfcht-v1.7 (commit 9f4a1b2); run scripts are containerized in Singularity (hash 3c7…9a1). Input decks, meshes, and outputs are tracked by DVC with SHA links to raw data. Unit tests for UDF I/O and mapping pass CI on each commit. This provides strong configuration management and regression evidence for a high-MRL application.</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2778,12 +2802,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Custom code components verified against analytical or manufactured solutions; energy conservation confirmed</t>
+          <t>The governing equations (conjugate heat transfer, Joule heating, Pennes perfusion) must be demonstrably solved correctly, supported by comparison to analytical or manufactured solutions.</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>Custom heat-source UDF and perfusion toggle verified against a closed-form (manufactured) temperature field with a tailored forcing source. Energy residual over the full control volume is &lt;0.2% at steady state. Unit tests for UDF I/O and mapping pass CI. This constitutes explicit code-level verification against analytical solutions for the non-standard physics components.</t>
+          <t>Custom heat-source UDF and perfusion toggle were exercised against a closed-form benchmark with a tailored forcing function. Control-volume energy residual was &lt;0.2% at steady state. Unit tests pass CI on each commit. This constitutes formal code verification against an analytical reference for the custom physics terms, with quantified residual error.</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2811,12 +2835,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Mesh convergence study with quantified discretization error; observed order consistent with scheme order; temporal convergence confirmed</t>
+          <t>Spatial and temporal discretization errors must be quantified and shown to be acceptable relative to validation tolerances and clinical decision margins.</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Four meshes from 1.2M to 9.6M cells with local refinement (min cell 20 µm at electrode/tissue interface). Observed order 1.96 consistent with second-order discretization. Richardson-extrapolated discretization effect: 3.8% on peak temperature, 2.6% on lesion depth. Time-step halving (5 ms → 2.5 ms) yields 0.6 C shift; 5 ms retained. Thorough quantification of both spatial and temporal discretization error.</t>
+          <t>Four meshes (1.2M–9.6M cells) with local refinement (min cell 20 µm) yielded observed convergence order 1.96 for peak temperature. Richardson-extrapolated discretization effect: 3.8% on peak temperature and 2.6% on lesion depth. Time-step halving (5 ms to 2.5 ms) produced only 0.6 C shift; 5 ms retained. Both spatial and temporal discretization errors are quantified and small relative to validation error bands.</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2837,19 +2861,19 @@
         </is>
       </c>
       <c r="C8" s="41" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="41" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>Residuals below specified targets; integral quantity convergence monitored</t>
+          <t>Iterative solver convergence must be demonstrated to be sufficient to avoid solver-induced error contaminating validation comparisons.</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Coupled solver residuals confirmed &lt;1e-6 for all equations. Integral energy balance monitored and plateaus within 0.3% over the last 10 s of each simulation. Both pointwise residuals and integral quantity convergence are documented, providing thorough evidence of solver convergence.</t>
+          <t>Residuals reported as &lt;1e-6. Integral energy balance monitored and plateaus within 0.3% over the last 10 s of each transient run. Coupled solver used. Convergence criteria are tight and monitored throughout the simulation.</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2877,12 +2901,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of model setup; boundary conditions and geometry verified; post-processing validated</t>
+          <t>Model setup (boundary conditions, geometry, mesh quality, post-processing) must be independently verified to be correct and consistent with the intended COU.</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>External SME Dr. R. Ghuman performed a red-team review of the full model setup and independently re-ran one case from scratch on a different workstation, reproducing results within 0.9 C and 0.3 mm. Two minor documentation action items were identified and closed. Boundary conditions (blood inflow, irrigation, RF power matching generator logs, esophageal isothermal BC) are documented and traceable. Vendor CAD used for geometry. Containerized workflow ensures reproducible setup.</t>
+          <t>External SME Dr. R. Ghuman performed a red-team review and independently re-ran one case from scratch on a different workstation, reproducing peak temperature within 0.9 C and lesion depth within 0.3 mm. Two minor documentation gaps identified were closed. Boundary conditions (blood inflow, irrigation rate, RF power via PI control matching generator logs) are documented and traceable. Configuration control via containerized workflow and DVC further reduces use-error risk.</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2910,12 +2934,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Governing equations justified for the physics regime; turbulence model sensitivity quantified; known model-form limitations documented</t>
+          <t>The mathematical model (governing equations, turbulence treatment, Joule heating, perfusion) must be justified and its known limitations documented relative to the COU.</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>3D conjugate thermal-fluid physics with Joule heating (temperature-dependent electrical conductivity), Pennes perfusion, and saline irrigation jets are documented and justified for the regime. Laminar assumption bracketed with SST k-omega sensitivity: turbulence model choice shifts peak temperature by &lt;1.2 C, included as a model-form bracket. Known limitations explicitly documented: no steam/char physics, homogeneous myocardium (no fiber anisotropy), simplified esophageal representation. One validation outlier at 45 W (char layer) highlights a documented model-form gap. Level 3 rather than 4 because the char/steam physics gap is unresolved and anisotropy is not quantified.</t>
+          <t>Physics basis is documented: incompressible flow with temperature-dependent properties, quasi-static electric field for Joule heating, temperature-dependent electrical conductivity (0.43–0.8 S/m), Pennes perfusion term. Turbulence model sensitivity bracketed (laminar vs SST k-omega; &lt;1.2 C shift). Known limitations explicitly documented: no steam/char physics, homogeneous myocardium (no fiber anisotropy), simplified esophageal boundary. However, the char-layer outlier at 45 W/0.15 m/s (15% depth under-prediction) is a recognized model-form gap. Full analytical justification for Pennes term applicability and constitutive model selection is not separately documented beyond the report text, limiting this to level 3.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2943,12 +2967,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties characterized with uncertainty; boundary conditions from measurements; geometry from CAD; input uncertainties quantified</t>
+          <t>Key model inputs (material properties, boundary conditions, geometry) must be well-characterized with uncertainties quantified and traceable to measurements or authoritative sources.</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>Tissue thermal and electrical properties assigned with ±15% uncertainty about literature values. Electrical conductivity temperature-dependence (0.43–0.8 S/m) included. Thermal contact resistance calibrated from three training cases with Bayesian posterior (mean 7.5 kW/m²·K, 95% CI 5.8–9.3). Boundary conditions from measured generator logs (RF power), calibrated flow meters (±1%), and esophageal wall temperature constrained to 37.0±0.2 C. Geometry from vendor CAD. Contact pressure range (10–20 kPa) from benchtop measurement. All inputs propagated through LHS N=200 with Sobol indices identifying dominant drivers.</t>
+          <t>Geometry from vendor CAD. Contact pressure (10–20 kPa, 0.2–0.5 mm indentation) from benchtop measurements. Blood inflow, irrigation, and RF power from controlled test and generator logs. Tissue thermal/electrical properties varied ±15% about literature values in the UQ study. Esophageal wall temperature 37.0 ± 0.2 C. Thermal contact resistance calibrated with posterior mean and 95% CI (5.8–9.3 kW/m²·K). Latin Hypercube propagation (N=200) with Sobol sensitivity indices identifies dominant inputs. Input characterization is thorough and uncertainties are quantified.</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2976,12 +3000,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Adequate number of specimens; production-representative samples; statistical characterization of sample variability</t>
+          <t>Validation test articles must be representative of the COU, with adequate sample size and characterization.</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>12 porcine perfused-myocardium specimens used for blinded validation spanning the clinical operating envelope (25–45 W, 17–30 mL/min, two blood speeds). Three additional training cases used only for calibration and kept separate. 7T MRI with 0.2 mm voxels for lesion characterization. Samples are porcine (not human) myocardium, which is anatomically relevant but introduces a species gap. Sample size of 12 provides adequate but not comprehensive statistical coverage; no explicit power analysis or inter-specimen variability characterization reported. Level 3 reflects adequate but not fully characterized sample statistics.</t>
+          <t>12 porcine perfused-myocardium benchtop specimens used for validation (3 additional reserved for calibration/training only, model frozen before validation set processed). Specimens span the clinical power and irrigation envelope. Porcine myocardium is a recognized surrogate for human atrial tissue in RF ablation studies. However, no formal statistical power analysis or inter-specimen variability characterization is reported. Sample size of 12 is modest but provides coverage of the two-dimensional input envelope. Tissue homogeneity assumed; no fiber-anisotropy characterization.</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -3009,12 +3033,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instruments; controlled and documented test conditions; measurement uncertainties quantified; test standards referenced</t>
+          <t>Test conditions must be controlled and instrumented with calibrated equipment and documented measurement uncertainties.</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Fiber-optic temperature probes with measurement uncertainty ±0.3 C (k=2, i.e., 95% CI). Lesion dimensions from 7T MRI at 0.2 mm voxel resolution with ±0.2 mm uncertainty. Flow controlled and measured to ±1%. Instrument calibration certificates attached to the record. Bath and probe logs archived. Blood speed set at two controlled values (0.15 and 0.25 m/s). Blinded validation data delivery after model freeze. RF power matched to generator logs. Well-documented, controlled benchtop environment with quantified measurement uncertainties.</t>
+          <t>Fiber-optic probes at 3 mm and 5 mm with ±0.3 C (k=2) calibrated uncertainty. Lesion dimensions from 7T MRI at 0.2 mm voxel resolution with ±0.2 mm uncertainty. Flow controlled with ±1% uncertainty. Instrument calibrations attached to the report. Bath and probe logs archived. Blinded validation data delivery (lab team provided files after model was frozen) reduces confirmation bias. Test conditions are well-controlled with quantified uncertainties.</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -3042,12 +3066,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model inputs matched to experimental conditions; measurement uncertainties propagated into comparison; boundary condition correspondence documented</t>
+          <t>Model inputs used in validation simulations must be matched to the measured experimental conditions with uncertainty propagated through the comparison.</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Model boundary conditions directly derived from recorded test conditions: blood inflow speed (0.15, 0.25 m/s), irrigation rate (17–30 mL/min ±1%), applied RF power matched to generator logs with PI control, esophageal wall temperature 37.0±0.2 C, contact pressure from benchtop measurements. Instrument calibration uncertainties (±0.3 C, ±1% flow, ±0.2 mm lesion) are propagated into the combined 95% total-error band used for comparison. LHS UQ propagation (N=200) maps input uncertainties to output uncertainty bands used in the output comparison.</t>
+          <t>Boundary conditions in simulation (blood inflow 0.15–0.30 m/s, irrigation 17–30 mL/min, RF power 25–45 W via PI control matching generator logs, esophageal wall 37.0±0.2 C) are explicitly matched to test conditions. Contact pressure (10–20 kPa) from benchtop measurements used directly. Measurement uncertainties (flow ±1%, temperature ±0.3 C k=2, dimensions ±0.2 mm) are propagated into the total-error band used for pass/fail assessment. Calibrated contact conductance (posterior mean with 95% CI) accounts for the dominant uncertain interface parameter.</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -3075,12 +3099,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative comparison metrics reported; multiple QoIs compared; uncertainty bands on both model and experiment; systematic outlier analysis</t>
+          <t>Model predictions must be compared quantitatively to experimental data with metrics, uncertainty bands, and pre-specified acceptance criteria.</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Three QoIs compared quantitatively: (1) tissue temperature at 3 mm depth — mean absolute error 2.1 C, 95th percentile error 4.0 C; (2) lesion depth NRMSE 9%; (3) lesion width NRMSE 11%. All 12 validation cases assessed against a pre-specified 95% total-error band combining model and test uncertainty. One outlier at 45 W/0.15 m/s (15% depth under-prediction) identified and attributed to char layer (documented model-form limitation). Combined UQ bands from LHS N=200. Temperature also compared at 5 mm depth (probe data collected). Multiple metrics, pre-specified acceptance criterion, and outlier root-cause analysis constitute thorough output comparison.</t>
+          <t>Multiple quantitative metrics reported: mean absolute temperature error 2.1 C, 95th-percentile 4.0 C at 3 mm; NRMSE on lesion depth 9%, width 11%. All 12 validation cases fall within the pre-specified 95% total-error band (combining model and test uncertainty). One outlier at 45 W/0.15 m/s flagged and explained (char layer). Comparison is multi-output (temperature field + two geometric dimensions). Training/validation sets are separated. Independent reproducibility check (Dr. Ghuman) confirms result stability. Pre-specified acceptance criteria from modeling plan are referenced.</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3108,12 +3132,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly measure the clinical safety/performance concern; measurable both computationally and experimentally</t>
+          <t>The model QoIs (peak temperature at 3 mm, lesion depth/width) must directly correspond to the clinical safety and efficacy metrics driving the IFU power/irrigation table.</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Peak tissue temperature at 3 mm depth directly corresponds to the thermal injury risk to adjacent esophageal tissue — the primary safety concern. Lesion depth and width characterize therapeutic efficacy. Both QoIs are directly measurable in the benchtop experiments (fiber-optic probes, 7T MRI) and are direct model outputs. The IFU power/irrigation table is derived from these same QoIs. High relevance with direct traceability from model output to clinical decision metric.</t>
+          <t>The two primary QoIs — peak tissue temperature at 3 mm depth and lesion depth/width after 30–60 s — are directly the clinical decision metrics for setting safe power/irrigation limits and avoiding thermal injury. Both are measurable computationally and experimentally (fiber-optic probes and 7T MRI). The esophageal proximity concern is captured via the esophageal boundary condition. QoIs are directly tied to the regulatory and safety consequences documented in the report.</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3141,12 +3165,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions span the clinical operating envelope; same geometry, physics regime, and tissue type; gaps to full COU documented</t>
+          <t>Validation conditions must cover the full intended clinical operating envelope; any gaps must be documented and addressed with margins or additional studies.</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation envelope (25–45 W, 17–30 mL/min, 0.15–0.25 m/s blood speed) covers the intended clinical range. Same catheter geometry, contact angles, and electrode configuration used. Porcine myocardium is anatomically representative. However, key gaps exist: (1) validation is benchtop only — no in vivo data yet (two in vivo checks deferred to next quarter); (2) esophageal proximity interaction not directly validated in the benchtop setup (isothermal BC assumption); (3) no validation at clinical contact forces above 20 g (clinical range extends to 30 g); (4) charring/steam-pop regime excluded. These documented gaps reduce applicability confidence below Level 4; pending in vivo data would be needed for full Level 4.</t>
+          <t>Validated envelope (25–45 W, 17–30 mL/min, blood speed 0.15–0.25 m/s) matches the intended clinical envelope. Geometry (7F catheter, 15° contact angle, 10–30 g contact force) is representative. Porcine benchtop surrogate does not replicate in vivo atrial anatomy, blood perfusion dynamics, or fibrotic tissue. Explicitly excluded from validation scope: steam pops, charring, highly trabeculated surfaces, fiber anisotropy. Two in vivo validation points are pending. The 5 C safety margin is proposed to account for these gaps. Applicability is good within the tested envelope but the absence of in vivo data and the char-layer model-form gap limit this to level 3.</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3235,7 +3259,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The CHT model meets or exceeds the evidence targets established in the modeling plan for MRL 4 / high-consequence use. Verification is thorough: custom UDF verified against manufactured solutions, four-level mesh convergence with quantified discretization errors (3.8% peak temp, 2.6% lesion depth), temporal convergence confirmed, and residuals &lt;1e-6. Validation against 12 blinded porcine benchtop cases demonstrates mean absolute temperature error of 2.1 C and lesion NRMSE ≤11%, with all cases within the pre-specified 95% total-error band except one char-layer outlier with documented root cause. UQ via LHS N=200 with Sobol sensitivity analysis identifies and quantifies dominant input drivers. Independent red-team reproduction confirms results within 0.9 C. The model is accepted for use in generating the IFU power/irrigation table within the validated envelope (25–45 W, 17–30 mL/min, 0.15–0.25 m/s, 10–30 g contact force), subject to the following conditions: (1) a 5 C safety margin is retained on the 3 mm temperature threshold; (2) the containerized workflow and DVC data tracking are maintained; (3) steam/char, fiber anisotropy, and highly trabeculated surface regimes are explicitly excluded from the IFU claims; and (4) the two planned in vivo validation points are added to the next validation update cycle.</t>
+          <t>The credibility evidence meets or exceeds the targets set in the V&amp;V plan for an MRL 4 / high-consequence application. Robust mesh and time-step convergence studies quantify discretization error (3.8% and 2.6% respectively). UDF and solver are formally verified against analytical benchmarks. Blinded validation against 12 independent porcine benchtop specimens shows mean absolute temperature error of 2.1 C and NRMSE on lesion dimensions of 9–11%, all within pre-specified 95% total-error bands. Input uncertainties are propagated via LHS (N=200) with Sobol sensitivity analysis identifying dominant parameters. Configuration control (Git, DVC, Singularity container), blinded data handling, and independent reproducibility review (Dr. Ghuman) are in place. Known model-form limitations (no charring/steam physics, homogeneous myocardium, simplified esophageal representation) are explicitly documented. Model is accepted for use in setting the IFU power/irrigation table within the validated envelope (25–45 W, 17–30 mL/min, blood speed 0.15–0.25 m/s, contact force 10–30 g), subject to: (1) a mandatory 5 C safety margin applied to the 3 mm peak-temperature threshold, (2) the containerized workflow maintained under current configuration control, and (3) completion of two in vivo validation points in the next quarter with results incorporated into the subsequent validation update before any expansion of the validated envelope.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -3248,7 +3272,11 @@
           <t>Dr. K. Alvarez, Program Lead</t>
         </is>
       </c>
-      <c r="E3" s="22" t="n"/>
+      <c r="E3" s="39" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="24" t="n"/>
